--- a/docs/PRAP_Server_Development_Plan_v0.1.xlsx
+++ b/docs/PRAP_Server_Development_Plan_v0.1.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>PARALLEL, NOT SUCCESSOR. Neither existing edition is retired by this. Both keep their own plans, gates and releases: PRAP_Development_Plan_v2.51.xlsx and PRAP_NewApp_Development_Plan_v1.13.xlsx.</t>
+          <t>PARALLEL, NOT SUCCESSOR. Neither existing edition is retired by this. Both keep their own plans, gates and releases: PRAP_Development_Plan_v2.51.xlsx and PRAP_NewApp_Development_Plan_v1.14.xlsx.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_Server_Development_Plan_v0.1.xlsx
+++ b/docs/PRAP_Server_Development_Plan_v0.1.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>PARALLEL, NOT SUCCESSOR. Neither existing edition is retired by this. Both keep their own plans, gates and releases: PRAP_Development_Plan_v2.51.xlsx and PRAP_NewApp_Development_Plan_v1.14.xlsx.</t>
+          <t>PARALLEL, NOT SUCCESSOR. Neither existing edition is retired by this. Both keep their own plans, gates and releases: PRAP_Development_Plan_v2.51.xlsx and PRAP_NewApp_Development_Plan_v1.15.xlsx.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_Server_Development_Plan_v0.1.xlsx
+++ b/docs/PRAP_Server_Development_Plan_v0.1.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Options" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Reuse" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Today" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Gaps" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Architecture" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Work" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Cost" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Risks" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Not_Proposed" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Questions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="00_Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01_Options" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_Reuse" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_Today" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05_Architecture" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="06_Work" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="07_Cost" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="08_Risks" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="09_Not_Proposed" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10_Questions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>PARALLEL, NOT SUCCESSOR. Neither existing edition is retired by this. Both keep their own plans, gates and releases: PRAP_Development_Plan_v2.51.xlsx and PRAP_NewApp_Development_Plan_v1.15.xlsx.</t>
+          <t>PARALLEL, NOT SUCCESSOR. Neither existing edition is retired by this. Both keep their own plans, gates and releases: PRAP_Development_Plan_v2.51.xlsx and PRAP_NewApp_Development_Plan_v1.16.xlsx.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_Server_Development_Plan_v0.1.xlsx
+++ b/docs/PRAP_Server_Development_Plan_v0.1.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>PARALLEL, NOT SUCCESSOR. Neither existing edition is retired by this. Both keep their own plans, gates and releases: PRAP_Development_Plan_v2.51.xlsx and PRAP_NewApp_Development_Plan_v1.16.xlsx.</t>
+          <t>PARALLEL, NOT SUCCESSOR. Neither existing edition is retired by this. Both keep their own plans, gates and releases: PRAP_Development_Plan_v2.51.xlsx and PRAP_NewApp_Development_Plan_v1.17.xlsx.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_Server_Development_Plan_v0.1.xlsx
+++ b/docs/PRAP_Server_Development_Plan_v0.1.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>PARALLEL, NOT SUCCESSOR. Neither existing edition is retired by this. Both keep their own plans, gates and releases: PRAP_Development_Plan_v2.51.xlsx and PRAP_NewApp_Development_Plan_v1.17.xlsx.</t>
+          <t>PARALLEL, NOT SUCCESSOR. Neither existing edition is retired by this. Both keep their own plans, gates and releases: PRAP_Development_Plan_v2.51.xlsx and PRAP_NewApp_Development_Plan_v1.18.xlsx.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_Server_Development_Plan_v0.1.xlsx
+++ b/docs/PRAP_Server_Development_Plan_v0.1.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="00_Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_Options" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_Reuse" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_Today" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_Gaps" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="05_Architecture" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="06_Work" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="07_Cost" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08_Risks" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="09_Not_Proposed" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="10_Questions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Options" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Reuse" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Today" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Architecture" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Work" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Cost" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Risks" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Not_Proposed" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Questions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
